--- a/output/pdf_financials_xlsx/GLB.xlsx
+++ b/output/pdf_financials_xlsx/GLB.xlsx
@@ -6188,43 +6188,43 @@
         <v>2.285859</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.285859</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.063127</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>6.326677</v>
       </c>
     </row>
     <row r="93">
@@ -7719,49 +7719,49 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.37819</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.21946</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.227654</v>
+        <v>0.130949</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.004337</v>
+        <v>0.003962</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.003964</v>
+        <v>-0.007627</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.005853</v>
+        <v>-0.010497</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.007192</v>
+        <v>-0.045228</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.005035</v>
+        <v>-0.22645</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.003524</v>
+        <v>-0.023888</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.002467</v>
+        <v>-0.029694</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.001727</v>
+        <v>-0.00378</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.001209</v>
+        <v>-0.011646</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004897</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.31487</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.003537</v>
+        <v>-0.013581</v>
       </c>
       <c r="S118" s="3" t="n">
         <v>0.00318</v>
@@ -10192,7 +10192,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10296,7 +10300,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10664,7 +10672,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -12114,7 +12126,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13986,7 +14002,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15166,7 +15186,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -22216,7 +22240,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -29512,7 +29540,11 @@
           <t>Exploration and evaluation of assets expenditures</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLB.xlsx
+++ b/output/pdf_financials_xlsx/GLB.xlsx
@@ -961,46 +961,46 @@
         <v>0.48699</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.605473</v>
+        <v>0.905881</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.665758</v>
+        <v>0.783447</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.856133</v>
+        <v>0.948619</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.135008</v>
+        <v>1.339127</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.441127</v>
+        <v>1.560536</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.737383</v>
+        <v>1.803515</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2.001579</v>
+        <v>2.057094</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.553135</v>
+        <v>0.60912</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.445401</v>
+        <v>1.503718</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.774428</v>
+        <v>1.820261</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>2.180547</v>
+        <v>2.263553</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.21929</v>
+        <v>2.837531</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.177806</v>
+        <v>2.557338</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.232119</v>
+        <v>6.451207</v>
       </c>
     </row>
     <row r="11">
@@ -1035,37 +1035,37 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.135008</v>
+        <v>-1.339127</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.441127</v>
+        <v>-1.560536</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.737383</v>
+        <v>-1.803515</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-2.001579</v>
+        <v>-2.057094</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.553135</v>
+        <v>-0.60912</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-1.445401</v>
+        <v>-1.503718</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.774428</v>
+        <v>-1.820261</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.180547</v>
+        <v>-2.263553</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.21929</v>
+        <v>-2.837531</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.177806</v>
+        <v>-2.557338</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.232119</v>
+        <v>-6.451207</v>
       </c>
     </row>
     <row r="12">
@@ -2511,58 +2511,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.012765</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.010399</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000499</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001092</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.052264</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003049</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.011254</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.008248</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.293645</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.496505</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.019636</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.044925</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.021922</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.032524</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.006282</v>
       </c>
     </row>
     <row r="35">
@@ -2633,58 +2633,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005592</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.012765</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.010399</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000499</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.077</v>
+        <v>0.07809199999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.036667</v>
+        <v>0.088931</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.12</v>
+        <v>0.123049</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.341254</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.255</v>
+        <v>0.263248</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.293645</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.496505</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.019636</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.044925</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.021922</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.032524</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.006282</v>
       </c>
     </row>
     <row r="37">
@@ -3365,58 +3365,58 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.013454</v>
+        <v>0.008354</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.017051</v>
+        <v>0.011459</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.005592</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.014998</v>
+        <v>0.002233</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000499</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.052264</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.003049</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.011254</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.018495</v>
+        <v>0.010247</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.386346</v>
+        <v>0.09270100000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.864595</v>
+        <v>0.36809</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.369357</v>
+        <v>0.349721</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.23325</v>
+        <v>0.188325</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.115527</v>
+        <v>0.09360499999999999</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.218503</v>
+        <v>0.185979</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.524145</v>
+        <v>0.517863</v>
       </c>
     </row>
     <row r="49">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">

--- a/output/pdf_financials_xlsx/GLB.xlsx
+++ b/output/pdf_financials_xlsx/GLB.xlsx
@@ -769,7 +769,7 @@
         <v>0.168489</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.063329</v>
+        <v>0.134787</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.36447</v>
@@ -952,7 +952,7 @@
         <v>0.177294</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.06963900000000001</v>
+        <v>0.141097</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.372739</v>
@@ -19478,7 +19478,11 @@
           <t>Equipment – Note 3</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -19582,7 +19586,11 @@
           <t>Mineral properties – Note 4</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -19794,7 +19802,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -20004,7 +20016,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20108,7 +20124,11 @@
           <t>Contributed surplus – Note 5</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -51942,7 +51962,11 @@
           <t>Management fees – Note 7</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -52154,7 +52178,11 @@
           <t>Professional fees – Note 7</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -52362,7 +52390,11 @@
           <t>Rent – Note 7</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -52466,7 +52498,11 @@
           <t>Shareholder communication – Note 7</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLB.xlsx
+++ b/output/pdf_financials_xlsx/GLB.xlsx
@@ -7362,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.033606</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -27356,7 +27356,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLB.xlsx
+++ b/output/pdf_financials_xlsx/GLB.xlsx
@@ -4397,46 +4397,46 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.039988</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.312069</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.356107</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.254468</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.083163</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.08487</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.115062</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>6.377923</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>7.686706</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.011193</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.011193</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.574726</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>10.942773</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>13.198587</v>
       </c>
     </row>
     <row r="65">
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>-0.007565</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.019456</v>
+        <v>-0.032487</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0.003912</v>
@@ -6724,10 +6724,10 @@
         <v>-0.016052</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.028497</v>
       </c>
       <c r="S101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014338</v>
       </c>
     </row>
     <row r="102">
@@ -6987,7 +6987,7 @@
         <v>-0.002914851</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.455391</v>
+        <v>-0.468422</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.155045</v>
@@ -7029,10 +7029,10 @@
         <v>0.205375</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>1.661968</v>
+        <v>1.633471</v>
       </c>
       <c r="S106" s="3" t="n">
-        <v>2.703378</v>
+        <v>2.68904</v>
       </c>
     </row>
     <row r="107">
@@ -7362,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0.033606</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -21790,7 +21790,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -21894,7 +21898,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -27356,11 +27364,7 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>SaleOfPPE</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -29154,7 +29158,11 @@
           <t>Proceeds from share issuances 6</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -30206,7 +30214,11 @@
           <t>Write-off of GST recoverable</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -30964,7 +30976,11 @@
           <t>Write-off of GST recoverable</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
